--- a/data/trending_integrated_20260916_09.xlsx
+++ b/data/trending_integrated_20260916_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15150</v>
+        <v>3840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+1.13%</t>
+          <t>'+29.95%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>191</v>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="G2" t="n">
-        <v>279</v>
+        <v>637</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>14980</v>
+        <v>2955</v>
       </c>
       <c r="K2" t="n">
-        <v>15300</v>
+        <v>3840</v>
       </c>
       <c r="L2" t="n">
-        <v>15580</v>
+        <v>3840</v>
       </c>
       <c r="M2" t="n">
-        <v>15120</v>
+        <v>3840</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>5352425535</v>
+        <v>6511459650</v>
       </c>
       <c r="P2" t="n">
-        <v>36200</v>
+        <v>6900</v>
       </c>
       <c r="Q2" t="n">
-        <v>8920</v>
+        <v>1738</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국제유가 상승 및 관련주 폭등 기대감, 사우디 송유관 재가동 뉴스 및 지정학적 이슈(호르무즈 해협) 언급. 단기 급등 및 하락 가능성 시사.</t>
+          <t>미국 클래리티법 부결 소식과 함께 카카오, 라인야후 등 언급, 코인 관련 긍정적 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['국제유가', '폭등', '지정학']</t>
+          <t>['클래리티법', '미버스 코인', '카카오']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,67 +648,67 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1692000</v>
+        <v>3945</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+12.23%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>483</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>315</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>1537</v>
+        <v>169</v>
       </c>
       <c r="H3" t="n">
-        <v>50.2</v>
+        <v>3.11</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1690000</v>
+        <v>3515</v>
       </c>
       <c r="K3" t="n">
-        <v>1686000</v>
+        <v>4120</v>
       </c>
       <c r="L3" t="n">
-        <v>1699000</v>
+        <v>4140</v>
       </c>
       <c r="M3" t="n">
-        <v>1686000</v>
+        <v>3840</v>
       </c>
       <c r="N3" t="n">
-        <v>50.27</v>
+        <v>3.16</v>
       </c>
       <c r="O3" t="n">
-        <v>134416639000</v>
+        <v>4408817708</v>
       </c>
       <c r="P3" t="n">
-        <v>2987000</v>
+        <v>16110</v>
       </c>
       <c r="Q3" t="n">
-        <v>331500</v>
+        <v>2300</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,20 +718,20 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미 증시 반도체 선물 상승 및 인텔 CEO 발언에도 불구하고, 매크로 지표 및 반도체 주 하락 가능성 언급. 일부 긍정적 전망과 부정적 예측 혼재.</t>
+          <t>25-26년 대규모 적자 예상 및 상폐 가능성 언급, 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '매크로']</t>
+          <t>['적자', '상폐', '임상']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,67 +740,67 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32350</v>
+        <v>1702000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-0.31%</t>
+          <t>'+0.71%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.34</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>530</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>338</v>
       </c>
       <c r="G4" t="n">
-        <v>407</v>
+        <v>1616</v>
       </c>
       <c r="H4" t="n">
-        <v>17.16</v>
+        <v>50.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>32450</v>
+        <v>1690000</v>
       </c>
       <c r="K4" t="n">
-        <v>32850</v>
+        <v>1686000</v>
       </c>
       <c r="L4" t="n">
-        <v>32850</v>
+        <v>1710000</v>
       </c>
       <c r="M4" t="n">
-        <v>32200</v>
+        <v>1686000</v>
       </c>
       <c r="N4" t="n">
-        <v>17.5</v>
+        <v>50.27</v>
       </c>
       <c r="O4" t="n">
-        <v>722321700</v>
+        <v>371269314000</v>
       </c>
       <c r="P4" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q4" t="n">
-        <v>24150</v>
+        <v>331500</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,29 +810,489 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>간암 신약 관련 유럽 품목 허가 신청 뉴스에 대한 상반된 해석. 성공 자신감 표현과 실패/지연 가능성, 투매/폭탄돌리기 경고 등 분석 엇갈림.</t>
+          <t>미 증시 반도체 선물 상승 및 인텔 CEO 발언에도 불구하고, 매크로 지표 및 반도체 주 하락 가능성 언급. 일부 긍정적 전망과 부정적 예측 혼재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['반도체', '선물', '매크로']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>72</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>흥구석유</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>15020</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'+0.27%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>115</v>
+      </c>
+      <c r="F5" t="n">
+        <v>73</v>
+      </c>
+      <c r="G5" t="n">
+        <v>320</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>14980</v>
+      </c>
+      <c r="K5" t="n">
+        <v>15300</v>
+      </c>
+      <c r="L5" t="n">
+        <v>15580</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14980</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>10393895160</v>
+      </c>
+      <c r="P5" t="n">
+        <v>36200</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8920</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>사우디 관련 국제유가 급등 및 미국 에너지주 폭등으로 인한 상승 기대감, 파병 이슈 언급.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['국제유가', '에너지주', '파병']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>024060</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>248500</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'+0.00%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E6" t="n">
+        <v>524</v>
+      </c>
+      <c r="F6" t="n">
+        <v>331</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2036</v>
+      </c>
+      <c r="H6" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>248500</v>
+      </c>
+      <c r="K6" t="n">
+        <v>248000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>249500</v>
+      </c>
+      <c r="M6" t="n">
+        <v>247500</v>
+      </c>
+      <c r="N6" t="n">
+        <v>46.57</v>
+      </c>
+      <c r="O6" t="n">
+        <v>216270439500</v>
+      </c>
+      <c r="P6" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>76700</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>정치적 이슈와 반도체 지수 상승 언급 외 구체적 근거 부족.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>107</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>31950</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-1.54%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="E7" t="n">
+        <v>74</v>
+      </c>
+      <c r="F7" t="n">
+        <v>52</v>
+      </c>
+      <c r="G7" t="n">
+        <v>439</v>
+      </c>
+      <c r="H7" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>32450</v>
+      </c>
+      <c r="K7" t="n">
+        <v>32850</v>
+      </c>
+      <c r="L7" t="n">
+        <v>32850</v>
+      </c>
+      <c r="M7" t="n">
+        <v>31900</v>
+      </c>
+      <c r="N7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1494459250</v>
+      </c>
+      <c r="P7" t="n">
+        <v>69200</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>24150</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>간암 신약 실패 가능성 언급 및 유럽 담관암 신약 신청 관련 분석, FDA 실패 가능성 제기.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
         <v>0.3</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>['신약', '허가', '분석']</t>
-        </is>
-      </c>
-      <c r="X4" t="n">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['신약', 'FDA', 'EMA']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
         <v>2</v>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>84600</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-1.86%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E8" t="n">
+        <v>65</v>
+      </c>
+      <c r="F8" t="n">
+        <v>47</v>
+      </c>
+      <c r="G8" t="n">
+        <v>352</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>86200</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86200</v>
+      </c>
+      <c r="L8" t="n">
+        <v>86300</v>
+      </c>
+      <c r="M8" t="n">
+        <v>84400</v>
+      </c>
+      <c r="N8" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="O8" t="n">
+        <v>24144621700</v>
+      </c>
+      <c r="P8" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>웨스팅하우스 지분 인수 기대감 있으나, 거래량 동반한 상승은 미미.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['지분 인수', '공매도']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>아톤</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5820</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-7.77%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="E9" t="n">
+        <v>47</v>
+      </c>
+      <c r="F9" t="n">
+        <v>26</v>
+      </c>
+      <c r="G9" t="n">
+        <v>80</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>6310</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6390</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6450</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5760</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O9" t="n">
+        <v>16356856890</v>
+      </c>
+      <c r="P9" t="n">
+        <v>11370</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3300</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>미국 클래리티법 부결로 인한 영향 분석 및 공급 계약 언급, 장대 음봉으로 인한 하락 우려.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['양자내성암호', '클래리티법', '보안주']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>158430</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260916_09.xlsx
+++ b/data/trending_integrated_20260916_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="F2" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G2" t="n">
-        <v>637</v>
+        <v>676</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>6511459650</v>
+        <v>6720006210</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -619,7 +619,7 @@
         <v>1738</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-29000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3945</v>
+        <v>4000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.23%</t>
+          <t>'+13.80%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="H3" t="n">
         <v>3.11</v>
@@ -702,7 +702,7 @@
         <v>3.16</v>
       </c>
       <c r="O3" t="n">
-        <v>4408817708</v>
+        <v>6209837750</v>
       </c>
       <c r="P3" t="n">
         <v>16110</v>
@@ -711,23 +711,23 @@
         <v>2300</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-371000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>25-26년 대규모 적자 예상 및 상폐 가능성 언급, 주가 조작 의혹 제기.</t>
+          <t>25년 94억, 26년 95억 적자 등 심각한 재무 상태에 대한 우려가 제기되며 상폐 가능성 언급. 주가조작 의혹 및 적자 기업 발악에 대한 부정적 시각이 지배적.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['적자', '상폐', '임상']</t>
+          <t>['적자', '상폐', '주가조작']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1702000</v>
+        <v>14910</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.71%</t>
+          <t>'+5.45%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>530</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>338</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>1616</v>
+        <v>210</v>
       </c>
       <c r="H4" t="n">
-        <v>50.2</v>
+        <v>1.95</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1690000</v>
+        <v>14140</v>
       </c>
       <c r="K4" t="n">
-        <v>1686000</v>
+        <v>14420</v>
       </c>
       <c r="L4" t="n">
-        <v>1710000</v>
+        <v>15110</v>
       </c>
       <c r="M4" t="n">
-        <v>1686000</v>
+        <v>14300</v>
       </c>
       <c r="N4" t="n">
-        <v>50.27</v>
+        <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>371269314000</v>
+        <v>71915806940</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q4" t="n">
-        <v>331500</v>
+        <v>1272</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>93000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미 증시 반도체 선물 상승 및 인텔 CEO 발언에도 불구하고, 매크로 지표 및 반도체 주 하락 가능성 언급. 일부 긍정적 전망과 부정적 예측 혼재.</t>
+          <t>통신장비 섹터 전반의 강세 속에서 대한광통신은 14000원 지지선 확보 후 상승 출발. 미장 상황과 무관하게 상승할 것이라는 기대감이 높으며, 신내림 받은 듯한 상승세에 대한 기대감 표출.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '매크로']</t>
+          <t>['통신장비', '지지선', '상승세']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15020</v>
+        <v>1718000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.27%</t>
+          <t>'+1.66%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>115</v>
+        <v>577</v>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>365</v>
       </c>
       <c r="G5" t="n">
-        <v>320</v>
+        <v>1725</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>50.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14980</v>
+        <v>1690000</v>
       </c>
       <c r="K5" t="n">
-        <v>15300</v>
+        <v>1686000</v>
       </c>
       <c r="L5" t="n">
-        <v>15580</v>
+        <v>1719000</v>
       </c>
       <c r="M5" t="n">
-        <v>14980</v>
+        <v>1686000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>50.27</v>
       </c>
       <c r="O5" t="n">
-        <v>10393895160</v>
+        <v>561253196500</v>
       </c>
       <c r="P5" t="n">
-        <v>36200</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>8920</v>
+        <v>331500</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>사우디 관련 국제유가 급등 및 미국 에너지주 폭등으로 인한 상승 기대감, 파병 이슈 언급.</t>
+          <t>뉴욕 증시 반도체 선물 강세 및 인텔 CEO 발언으로 인한 긍정적 전망. JP모건의 SK하이닉스 ADR 매수 소식도 있으나, 일부 게시글에서는 매크로 지표 및 정치적 이슈로 인한 하락 가능성도 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['국제유가', '에너지주', '파병']</t>
+          <t>['반도체', '선물 강세', '매크로 지표']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>248500</v>
+        <v>249250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.30%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>524</v>
+        <v>565</v>
       </c>
       <c r="F6" t="n">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="G6" t="n">
-        <v>2036</v>
+        <v>2144</v>
       </c>
       <c r="H6" t="n">
         <v>46.56</v>
@@ -978,7 +978,7 @@
         <v>46.57</v>
       </c>
       <c r="O6" t="n">
-        <v>216270439500</v>
+        <v>289929289500</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -987,7 +987,7 @@
         <v>76700</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-375000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31950</v>
+        <v>14970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.54%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="F7" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>439</v>
+        <v>352</v>
       </c>
       <c r="H7" t="n">
-        <v>17.16</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>32450</v>
+        <v>14980</v>
       </c>
       <c r="K7" t="n">
-        <v>32850</v>
+        <v>15300</v>
       </c>
       <c r="L7" t="n">
-        <v>32850</v>
+        <v>15580</v>
       </c>
       <c r="M7" t="n">
-        <v>31900</v>
+        <v>14840</v>
       </c>
       <c r="N7" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1494459250</v>
+        <v>12982201405</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>36200</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>8920</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-49000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>간암 신약 실패 가능성 언급 및 유럽 담관암 신약 신청 관련 분석, FDA 실패 가능성 제기.</t>
+          <t>사우디 관련 이슈 및 국제 유가 상승과 맞물려 오일 관련주 폭등 기대감. 특히 파병 이슈와 맞물려 유가 급등 및 20% 이상 상승 시작 가능성 언급. 일부 비축유 관련 우려도 있으나 전반적으로 긍정적.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['신약', 'FDA', 'EMA']</t>
+          <t>['국제유가', '사우디', '폭등']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84600</v>
+        <v>84700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'-1.74%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
-        <v>352</v>
+        <v>383</v>
       </c>
       <c r="H8" t="n">
         <v>23.37</v>
@@ -1162,7 +1162,7 @@
         <v>23.45</v>
       </c>
       <c r="O8" t="n">
-        <v>24144621700</v>
+        <v>30329925200</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1171,23 +1171,23 @@
         <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-82000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 기대감 있으나, 거래량 동반한 상승은 미미.</t>
+          <t>웨스팅하우스 지분 인수 기대감과 공매도 움직임 속에서 상승세를 보이는 가운데, 10만원 돌파 및 외인 매수세 유입에 대한 기대감이 존재. 그러나 거래량 부진으로 인한 상승 동력 약화 우려도.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['지분 인수', '공매도']</t>
+          <t>['지분 인수', '공매도', '상승세']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5820</v>
+        <v>31700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-7.77%</t>
+          <t>'-2.31%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-2.04</v>
+        <v>-0.34</v>
       </c>
       <c r="E9" t="n">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>80</v>
+        <v>481</v>
       </c>
       <c r="H9" t="n">
-        <v>0.98</v>
+        <v>17.16</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6310</v>
+        <v>32450</v>
       </c>
       <c r="K9" t="n">
-        <v>6390</v>
+        <v>32850</v>
       </c>
       <c r="L9" t="n">
-        <v>6450</v>
+        <v>32850</v>
       </c>
       <c r="M9" t="n">
-        <v>5760</v>
+        <v>31700</v>
       </c>
       <c r="N9" t="n">
-        <v>3.02</v>
+        <v>17.5</v>
       </c>
       <c r="O9" t="n">
-        <v>16356856890</v>
+        <v>2269188675</v>
       </c>
       <c r="P9" t="n">
-        <v>11370</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>3300</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-19000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 클래리티법 부결로 인한 영향 분석 및 공급 계약 언급, 장대 음봉으로 인한 하락 우려.</t>
+          <t>간암 신약 관련 유럽 품목 허가 신청 소식이 있으나, 과거 실패 사례 및 유럽 신청 시점에 대한 의문 제기. FDA 승인 자신감 표현과 사기꾼 망할 것이라는 부정적 전망이 공존하며, 기관 및 외인 매도 가능성도 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['양자내성암호', '클래리티법', '보안주']</t>
+          <t>['신약 허가', 'FDA', '유럽 신청']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1291,6 +1291,98 @@
         </is>
       </c>
       <c r="Z9" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>아톤</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5790</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-8.24%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="E10" t="n">
+        <v>53</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G10" t="n">
+        <v>89</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>6310</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6390</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6450</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5740</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O10" t="n">
+        <v>19430714930</v>
+      </c>
+      <c r="P10" t="n">
+        <v>11370</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3300</v>
+      </c>
+      <c r="R10" t="n">
+        <v>213000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>미국 클래리티법 상원 부결 소식에도 불구하고, 삼성과의 대규모 공급 계약(4381억) 및 이스타항공 양자내성암호 OTP 공급 계약 체결. 그러나 가상자산 관련 규제 및 해킹 이슈, 공매도, 하한가 예상 등 부정적 요인도 존재.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['양자내성암호', '공급 계약', '가상자산']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>158430</t>
         </is>

--- a/data/trending_integrated_20260916_09.xlsx
+++ b/data/trending_integrated_20260916_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F2" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G2" t="n">
-        <v>676</v>
+        <v>712</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>6720006210</v>
+        <v>6796552770</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 클래리티법 부결 소식과 함께 카카오, 라인야후 등 언급, 코인 관련 긍정적 전망.</t>
+          <t>미투온, 미국 클래리티법 부결로 인한 가상자산 관련 기대감 상승. 합법 카지노 사업 확장 및 미버스 코인 급등세로 긍정적 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['클래리티법', '미버스 코인', '카카오']</t>
+          <t>['카지노', '미버스 코인', '클래리티법']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4000</v>
+        <v>3890</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.80%</t>
+          <t>'+10.67%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="H3" t="n">
         <v>3.11</v>
@@ -702,7 +702,7 @@
         <v>3.16</v>
       </c>
       <c r="O3" t="n">
-        <v>6209837750</v>
+        <v>7711412170</v>
       </c>
       <c r="P3" t="n">
         <v>16110</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>25년 94억, 26년 95억 적자 등 심각한 재무 상태에 대한 우려가 제기되며 상폐 가능성 언급. 주가조작 의혹 및 적자 기업 발악에 대한 부정적 시각이 지배적.</t>
+          <t>이뮨온시아, 25~26년 대규모 적자 예상 발표 후 주가 급락. 상폐 수준의 재무 상태 및 임상 성공 불확실성으로 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['적자', '상폐', '주가조작']</t>
+          <t>['적자', '상폐', '임상']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14910</v>
+        <v>15230</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.45%</t>
+          <t>'+7.71%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.15</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="H4" t="n">
         <v>1.95</v>
@@ -785,7 +785,7 @@
         <v>14420</v>
       </c>
       <c r="L4" t="n">
-        <v>15110</v>
+        <v>15250</v>
       </c>
       <c r="M4" t="n">
         <v>14300</v>
@@ -794,7 +794,7 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>71915806940</v>
+        <v>106547715075</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>통신장비 섹터 전반의 강세 속에서 대한광통신은 14000원 지지선 확보 후 상승 출발. 미장 상황과 무관하게 상승할 것이라는 기대감이 높으며, 신내림 받은 듯한 상승세에 대한 기대감 표출.</t>
+          <t>대한광통신, 통신장비 섹터 강세 속 상승 출발. 14000원 지지선 확보 및 기관 매수세 유입. 단타 활용 권유.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['통신장비', '지지선', '상승세']</t>
+          <t>['통신장비', '기관 매수', '지지선']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1718000</v>
+        <v>1715500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.66%</t>
+          <t>'+1.51%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>577</v>
+        <v>640</v>
       </c>
       <c r="F5" t="n">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="G5" t="n">
-        <v>1725</v>
+        <v>1851</v>
       </c>
       <c r="H5" t="n">
         <v>50.2</v>
@@ -877,7 +877,7 @@
         <v>1686000</v>
       </c>
       <c r="L5" t="n">
-        <v>1719000</v>
+        <v>1720000</v>
       </c>
       <c r="M5" t="n">
         <v>1686000</v>
@@ -886,7 +886,7 @@
         <v>50.27</v>
       </c>
       <c r="O5" t="n">
-        <v>561253196500</v>
+        <v>690333456500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>뉴욕 증시 반도체 선물 강세 및 인텔 CEO 발언으로 인한 긍정적 전망. JP모건의 SK하이닉스 ADR 매수 소식도 있으나, 일부 게시글에서는 매크로 지표 및 정치적 이슈로 인한 하락 가능성도 제기.</t>
+          <t>SK하이닉스, 뉴욕증시 반도체 선물 급등 및 인텔 CEO 발언에 따른 긍정적 전망. 매크로 지표 및 정부 정책 관련 우려도 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '선물 강세', '매크로 지표']</t>
+          <t>['반도체', '선물', '매크로']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>565</v>
+        <v>615</v>
       </c>
       <c r="F6" t="n">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="G6" t="n">
-        <v>2144</v>
+        <v>2207</v>
       </c>
       <c r="H6" t="n">
         <v>46.56</v>
@@ -969,7 +969,7 @@
         <v>248000</v>
       </c>
       <c r="L6" t="n">
-        <v>249500</v>
+        <v>250000</v>
       </c>
       <c r="M6" t="n">
         <v>247500</v>
@@ -978,7 +978,7 @@
         <v>46.57</v>
       </c>
       <c r="O6" t="n">
-        <v>289929289500</v>
+        <v>361695397000</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14970</v>
+        <v>8500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'-1.28%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E7" t="n">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>352</v>
+        <v>87</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>26.66</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14980</v>
+        <v>8610</v>
       </c>
       <c r="K7" t="n">
-        <v>15300</v>
+        <v>8600</v>
       </c>
       <c r="L7" t="n">
-        <v>15580</v>
+        <v>8610</v>
       </c>
       <c r="M7" t="n">
-        <v>14840</v>
+        <v>8460</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>27.16</v>
       </c>
       <c r="O7" t="n">
-        <v>12982201405</v>
+        <v>3812698150</v>
       </c>
       <c r="P7" t="n">
-        <v>36200</v>
+        <v>17950</v>
       </c>
       <c r="Q7" t="n">
-        <v>8920</v>
+        <v>8120</v>
       </c>
       <c r="R7" t="n">
-        <v>-49000</v>
+        <v>-150000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>사우디 관련 이슈 및 국제 유가 상승과 맞물려 오일 관련주 폭등 기대감. 특히 파병 이슈와 맞물려 유가 급등 및 20% 이상 상승 시작 가능성 언급. 일부 비축유 관련 우려도 있으나 전반적으로 긍정적.</t>
+          <t>LG디스플레이, 3분기 실적 및 주가 전망에 대한 엇갈린 분석. 배당 기대감 있으나 높은 부채 및 외인 매도세 우려. 저평가 논란.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['국제유가', '사우디', '폭등']</t>
+          <t>['PBR', '배당', '실적']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84700</v>
+        <v>85000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.74%</t>
+          <t>'-1.39%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
-        <v>383</v>
+        <v>422</v>
       </c>
       <c r="H8" t="n">
         <v>23.37</v>
@@ -1162,7 +1162,7 @@
         <v>23.45</v>
       </c>
       <c r="O8" t="n">
-        <v>30329925200</v>
+        <v>35882135100</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 기대감과 공매도 움직임 속에서 상승세를 보이는 가운데, 10만원 돌파 및 외인 매수세 유입에 대한 기대감이 존재. 그러나 거래량 부진으로 인한 상승 동력 약화 우려도.</t>
+          <t>두산에너빌리티, 웨스팅하우스 지분 인수 기대감 속에 공매도 세력과의 힘겨루기. 긍정적 발표 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['지분 인수', '공매도', '상승세']</t>
+          <t>['웨스팅하우스', '지분 인수', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31700</v>
+        <v>14740</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.31%</t>
+          <t>'-1.60%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="G9" t="n">
-        <v>481</v>
+        <v>345</v>
       </c>
       <c r="H9" t="n">
-        <v>17.16</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>32450</v>
+        <v>14980</v>
       </c>
       <c r="K9" t="n">
-        <v>32850</v>
+        <v>15300</v>
       </c>
       <c r="L9" t="n">
-        <v>32850</v>
+        <v>15580</v>
       </c>
       <c r="M9" t="n">
-        <v>31700</v>
+        <v>14700</v>
       </c>
       <c r="N9" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2269188675</v>
+        <v>14822472560</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>36200</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>8920</v>
       </c>
       <c r="R9" t="n">
-        <v>-19000</v>
+        <v>-49000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>간암 신약 관련 유럽 품목 허가 신청 소식이 있으나, 과거 실패 사례 및 유럽 신청 시점에 대한 의문 제기. FDA 승인 자신감 표현과 사기꾼 망할 것이라는 부정적 전망이 공존하며, 기관 및 외인 매도 가능성도 언급.</t>
+          <t>사우디 관련 이슈 및 국제 유가 상승과 맞물려 오일 관련주 폭등 기대감. 특히 파병 이슈와 맞물려 유가 급등 및 20% 이상 상승 시작 가능성 언급. 일부 비축유 관련 우려도 있으나 전반적으로 긍정적.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['신약 허가', 'FDA', '유럽 신청']</t>
+          <t>['국제유가', '사우디', '폭등']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5790</v>
+        <v>31750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-8.24%</t>
+          <t>'-2.16%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-2.04</v>
+        <v>-0.34</v>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="G10" t="n">
-        <v>89</v>
+        <v>550</v>
       </c>
       <c r="H10" t="n">
-        <v>0.98</v>
+        <v>17.16</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6310</v>
+        <v>32450</v>
       </c>
       <c r="K10" t="n">
-        <v>6390</v>
+        <v>32850</v>
       </c>
       <c r="L10" t="n">
-        <v>6450</v>
+        <v>32850</v>
       </c>
       <c r="M10" t="n">
-        <v>5740</v>
+        <v>31550</v>
       </c>
       <c r="N10" t="n">
-        <v>3.02</v>
+        <v>17.5</v>
       </c>
       <c r="O10" t="n">
-        <v>19430714930</v>
+        <v>2745810525</v>
       </c>
       <c r="P10" t="n">
-        <v>11370</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>3300</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>213000</v>
+        <v>-19000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 클래리티법 상원 부결 소식에도 불구하고, 삼성과의 대규모 공급 계약(4381억) 및 이스타항공 양자내성암호 OTP 공급 계약 체결. 그러나 가상자산 관련 규제 및 해킹 이슈, 공매도, 하한가 예상 등 부정적 요인도 존재.</t>
+          <t>HLB, 간암 신약 관련 유럽 담관암 신청에 대한 해석 엇갈림. FDA 실패 시 하한가 우려와 EMA 신청을 긍정적 신호로 보는 시각 공존.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['양자내성암호', '공급 계약', '가상자산']</t>
+          <t>['신약', 'FDA', 'EMA']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1383,6 +1383,98 @@
         </is>
       </c>
       <c r="Z10" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>아톤</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5650</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-10.46%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="E11" t="n">
+        <v>58</v>
+      </c>
+      <c r="F11" t="n">
+        <v>34</v>
+      </c>
+      <c r="G11" t="n">
+        <v>114</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>6310</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6390</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6450</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5630</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O11" t="n">
+        <v>23007399510</v>
+      </c>
+      <c r="P11" t="n">
+        <v>11370</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3300</v>
+      </c>
+      <c r="R11" t="n">
+        <v>213000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>아톤, 미국 클래리티법 부결로 인한 영향 및 삼성과의 대규모 공급 계약 사실 부각. 가상자산 관련 변동성 및 하한가 우려.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['OTP', '클래리티법', '공급계약']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>158430</t>
         </is>

--- a/data/trending_integrated_20260916_09.xlsx
+++ b/data/trending_integrated_20260916_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F2" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G2" t="n">
-        <v>712</v>
+        <v>730</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>6796552770</v>
+        <v>6842847810</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미투온, 미국 클래리티법 부결로 인한 가상자산 관련 기대감 상승. 합법 카지노 사업 확장 및 미버스 코인 급등세로 긍정적 전망.</t>
+          <t>미투온은 휴무일이며, 미버스코인 급등세와 관련된 언급이 존재합니다. 카카오 관련 내용도 일부 포함되어 있습니다.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['카지노', '미버스 코인', '클래리티법']</t>
+          <t>['미버스코인', '카카오', '주주변경']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3890</v>
+        <v>3895</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+10.67%</t>
+          <t>'+10.81%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="H3" t="n">
         <v>3.11</v>
@@ -702,7 +702,7 @@
         <v>3.16</v>
       </c>
       <c r="O3" t="n">
-        <v>7711412170</v>
+        <v>8370207734</v>
       </c>
       <c r="P3" t="n">
         <v>16110</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>이뮨온시아, 25~26년 대규모 적자 예상 발표 후 주가 급락. 상폐 수준의 재무 상태 및 임상 성공 불확실성으로 투자 심리 위축.</t>
+          <t>25-26년 대규모 적자 예상 및 상폐 가능성 제기. 주가 하락 및 투자 경고 신호.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['적자', '상폐', '임상']</t>
+          <t>['적자', '상폐', '하락']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15230</v>
+        <v>4480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.71%</t>
+          <t>'+8.74%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>223</v>
+        <v>87</v>
       </c>
       <c r="H4" t="n">
-        <v>1.95</v>
+        <v>0.74</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14140</v>
+        <v>4120</v>
       </c>
       <c r="K4" t="n">
-        <v>14420</v>
+        <v>4120</v>
       </c>
       <c r="L4" t="n">
-        <v>15250</v>
+        <v>4800</v>
       </c>
       <c r="M4" t="n">
-        <v>14300</v>
+        <v>4100</v>
       </c>
       <c r="N4" t="n">
-        <v>1.8</v>
+        <v>0.77</v>
       </c>
       <c r="O4" t="n">
-        <v>106547715075</v>
+        <v>153250673389</v>
       </c>
       <c r="P4" t="n">
-        <v>31500</v>
+        <v>8100</v>
       </c>
       <c r="Q4" t="n">
-        <v>1272</v>
+        <v>592</v>
       </c>
       <c r="R4" t="n">
-        <v>93000</v>
+        <v>384000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>대한광통신, 통신장비 섹터 강세 속 상승 출발. 14000원 지지선 확보 및 기관 매수세 유입. 단타 활용 권유.</t>
+          <t>광케이블 관련 미 증시 상승 수혜 및 4천원 지지선 언급. 7천원까지의 상승 가능성 및 외국인 매수세 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['통신장비', '기관 매수', '지지선']</t>
+          <t>['광케이블', '지지선', '외국인']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1715500</v>
+        <v>14820</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.51%</t>
+          <t>'+4.81%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>640</v>
+        <v>69</v>
       </c>
       <c r="F5" t="n">
-        <v>391</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>1851</v>
+        <v>255</v>
       </c>
       <c r="H5" t="n">
-        <v>50.2</v>
+        <v>1.95</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1690000</v>
+        <v>14140</v>
       </c>
       <c r="K5" t="n">
-        <v>1686000</v>
+        <v>14420</v>
       </c>
       <c r="L5" t="n">
-        <v>1720000</v>
+        <v>15250</v>
       </c>
       <c r="M5" t="n">
-        <v>1686000</v>
+        <v>14300</v>
       </c>
       <c r="N5" t="n">
-        <v>50.27</v>
+        <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>690333456500</v>
+        <v>132543511315</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>331500</v>
+        <v>1272</v>
       </c>
       <c r="R5" t="n">
-        <v>4000</v>
+        <v>93000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SK하이닉스, 뉴욕증시 반도체 선물 급등 및 인텔 CEO 발언에 따른 긍정적 전망. 매크로 지표 및 정부 정책 관련 우려도 혼재.</t>
+          <t>미 증시 통신장비주 강세에 따른 동반 상승 기대감. 14000원 지지선 확보 및 17000원 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '매크로']</t>
+          <t>['통신장비', '지지선', '상승']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>249250</v>
+        <v>1726000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.30%</t>
+          <t>'+2.13%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>615</v>
+        <v>677</v>
       </c>
       <c r="F6" t="n">
-        <v>369</v>
+        <v>414</v>
       </c>
       <c r="G6" t="n">
-        <v>2207</v>
+        <v>2010</v>
       </c>
       <c r="H6" t="n">
-        <v>46.56</v>
+        <v>50.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>248500</v>
+        <v>1690000</v>
       </c>
       <c r="K6" t="n">
-        <v>248000</v>
+        <v>1686000</v>
       </c>
       <c r="L6" t="n">
-        <v>250000</v>
+        <v>1729000</v>
       </c>
       <c r="M6" t="n">
-        <v>247500</v>
+        <v>1686000</v>
       </c>
       <c r="N6" t="n">
-        <v>46.57</v>
+        <v>50.27</v>
       </c>
       <c r="O6" t="n">
-        <v>361695397000</v>
+        <v>871408434500</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>76700</v>
+        <v>331500</v>
       </c>
       <c r="R6" t="n">
-        <v>-375000</v>
+        <v>4000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 이슈와 반도체 지수 상승 언급 외 구체적 근거 부족.</t>
+          <t>미 증시 반도체 선물 상승 및 인텔 CEO 발언에 대한 기대감 존재. 다만, 매크로 지표 및 반도체 주 하락 가능성에 대한 신중론도 제기됨.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['반도체', '선물', '전망']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8500</v>
+        <v>250500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.28%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.5</v>
+        <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>654</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>392</v>
       </c>
       <c r="G7" t="n">
-        <v>87</v>
+        <v>2252</v>
       </c>
       <c r="H7" t="n">
-        <v>26.66</v>
+        <v>46.56</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8610</v>
+        <v>248500</v>
       </c>
       <c r="K7" t="n">
-        <v>8600</v>
+        <v>248000</v>
       </c>
       <c r="L7" t="n">
-        <v>8610</v>
+        <v>251000</v>
       </c>
       <c r="M7" t="n">
-        <v>8460</v>
+        <v>247500</v>
       </c>
       <c r="N7" t="n">
-        <v>27.16</v>
+        <v>46.57</v>
       </c>
       <c r="O7" t="n">
-        <v>3812698150</v>
+        <v>469646632500</v>
       </c>
       <c r="P7" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>8120</v>
+        <v>76700</v>
       </c>
       <c r="R7" t="n">
-        <v>-150000</v>
+        <v>-375000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>LG디스플레이, 3분기 실적 및 주가 전망에 대한 엇갈린 분석. 배당 기대감 있으나 높은 부채 및 외인 매도세 우려. 저평가 논란.</t>
+          <t>정치적 이슈와 반도체 지수 상승 언급 외 구체적 근거 부족.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['PBR', '배당', '실적']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85000</v>
+        <v>3385</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.39%</t>
+          <t>'+0.74%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.08</v>
+        <v>-1.34</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>422</v>
+        <v>101</v>
       </c>
       <c r="H8" t="n">
-        <v>23.37</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>86200</v>
+        <v>3360</v>
       </c>
       <c r="K8" t="n">
-        <v>86200</v>
+        <v>3570</v>
       </c>
       <c r="L8" t="n">
-        <v>86300</v>
+        <v>3910</v>
       </c>
       <c r="M8" t="n">
-        <v>84400</v>
+        <v>3345</v>
       </c>
       <c r="N8" t="n">
-        <v>23.45</v>
+        <v>1.34</v>
       </c>
       <c r="O8" t="n">
-        <v>35882135100</v>
+        <v>69248669108</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>5100</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>966</v>
       </c>
       <c r="R8" t="n">
-        <v>-82000</v>
+        <v>592000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 웨스팅하우스 지분 인수 기대감 속에 공매도 세력과의 힘겨루기. 긍정적 발표 가능성 언급.</t>
+          <t>양자내성암호 관련 이슈 부각. 다만, 단기 급등 후 하락 가능성 및 분기 매출 부진에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '지분 인수', '공매도']</t>
+          <t>['양자암호', '매출', '하락']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14740</v>
+        <v>8500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.60%</t>
+          <t>'-1.28%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E9" t="n">
-        <v>131</v>
+        <v>52</v>
       </c>
       <c r="F9" t="n">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>345</v>
+        <v>128</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>26.66</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14980</v>
+        <v>8610</v>
       </c>
       <c r="K9" t="n">
-        <v>15300</v>
+        <v>8600</v>
       </c>
       <c r="L9" t="n">
-        <v>15580</v>
+        <v>8610</v>
       </c>
       <c r="M9" t="n">
-        <v>14700</v>
+        <v>8460</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>27.16</v>
       </c>
       <c r="O9" t="n">
-        <v>14822472560</v>
+        <v>4118565445</v>
       </c>
       <c r="P9" t="n">
-        <v>36200</v>
+        <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>8920</v>
+        <v>8120</v>
       </c>
       <c r="R9" t="n">
-        <v>-49000</v>
+        <v>-150000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>사우디 관련 이슈 및 국제 유가 상승과 맞물려 오일 관련주 폭등 기대감. 특히 파병 이슈와 맞물려 유가 급등 및 20% 이상 상승 시작 가능성 언급. 일부 비축유 관련 우려도 있으나 전반적으로 긍정적.</t>
+          <t>키움 리포트 기반 3분기 실적 하락 가능성 언급. 외인 매도세 및 높은 부채 비율 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['국제유가', '사우디', '폭등']</t>
+          <t>['실적', '환율', '부채']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31750</v>
+        <v>84900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.16%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.34</v>
+        <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F10" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G10" t="n">
-        <v>550</v>
+        <v>418</v>
       </c>
       <c r="H10" t="n">
-        <v>17.16</v>
+        <v>23.37</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>32450</v>
+        <v>86200</v>
       </c>
       <c r="K10" t="n">
-        <v>32850</v>
+        <v>86200</v>
       </c>
       <c r="L10" t="n">
-        <v>32850</v>
+        <v>86300</v>
       </c>
       <c r="M10" t="n">
-        <v>31550</v>
+        <v>84400</v>
       </c>
       <c r="N10" t="n">
-        <v>17.5</v>
+        <v>23.45</v>
       </c>
       <c r="O10" t="n">
-        <v>2745810525</v>
+        <v>39105566550</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>-19000</v>
+        <v>-82000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>HLB, 간암 신약 관련 유럽 담관암 신청에 대한 해석 엇갈림. FDA 실패 시 하한가 우려와 EMA 신청을 긍정적 신호로 보는 시각 공존.</t>
+          <t>웨스팅하우스 지분 인수 가능성에 대한 기대감과 공매도 관련 우려가 혼재. 대규모 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['신약', 'FDA', 'EMA']</t>
+          <t>['지분 인수', '공매도', '전망']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5650</v>
+        <v>14700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-10.46%</t>
+          <t>'-1.87%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-2.04</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="G11" t="n">
-        <v>114</v>
+        <v>363</v>
       </c>
       <c r="H11" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6310</v>
+        <v>14980</v>
       </c>
       <c r="K11" t="n">
-        <v>6390</v>
+        <v>15300</v>
       </c>
       <c r="L11" t="n">
-        <v>6450</v>
+        <v>15580</v>
       </c>
       <c r="M11" t="n">
-        <v>5630</v>
+        <v>14610</v>
       </c>
       <c r="N11" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>23007399510</v>
+        <v>16218854420</v>
       </c>
       <c r="P11" t="n">
-        <v>11370</v>
+        <v>36200</v>
       </c>
       <c r="Q11" t="n">
-        <v>3300</v>
+        <v>8920</v>
       </c>
       <c r="R11" t="n">
-        <v>213000</v>
+        <v>-49000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>아톤, 미국 클래리티법 부결로 인한 영향 및 삼성과의 대규모 공급 계약 사실 부각. 가상자산 관련 변동성 및 하한가 우려.</t>
+          <t>국제유가 상승 및 이란 관련 지정학적 리스크 부각. 1만 5천원대 이상 상승 여력 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,18 +1463,202 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['OTP', '클래리티법', '공급계약']</t>
+          <t>['국제유가', '지정학적 리스크', '상승']</t>
         </is>
       </c>
       <c r="X11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>024060</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>31650</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-2.47%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="E12" t="n">
+        <v>106</v>
+      </c>
+      <c r="F12" t="n">
+        <v>72</v>
+      </c>
+      <c r="G12" t="n">
+        <v>599</v>
+      </c>
+      <c r="H12" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>32450</v>
+      </c>
+      <c r="K12" t="n">
+        <v>32850</v>
+      </c>
+      <c r="L12" t="n">
+        <v>32850</v>
+      </c>
+      <c r="M12" t="n">
+        <v>31550</v>
+      </c>
+      <c r="N12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3010157300</v>
+      </c>
+      <c r="P12" t="n">
+        <v>69200</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>24150</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-19000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>간암 신약 관련 유럽 신청 결과 및 FDA 승인 실패 가능성에 대한 우려. 과거 실패 사례 및 주가 하락 가능성 언급.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['신약', 'FDA', '실패']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>2</v>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>아톤</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5740</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-9.03%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="E13" t="n">
+        <v>62</v>
+      </c>
+      <c r="F13" t="n">
+        <v>37</v>
+      </c>
+      <c r="G13" t="n">
+        <v>112</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>6310</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6390</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6450</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5630</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O13" t="n">
+        <v>25798576330</v>
+      </c>
+      <c r="P13" t="n">
+        <v>11370</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3300</v>
+      </c>
+      <c r="R13" t="n">
+        <v>213000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>미 클래리티법 부결 및 이스타항공 공급 계약 소식에도 불구하고, 삼성과의 공급 계약 규모 및 가상자산 시장 약세 영향.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['양자내성암호', '공급계약', '가상자산']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>158430</t>
         </is>

--- a/data/trending_integrated_20260916_09.xlsx
+++ b/data/trending_integrated_20260916_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-1.21</v>
       </c>
       <c r="E2" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G2" t="n">
-        <v>730</v>
+        <v>753</v>
       </c>
       <c r="H2" t="n">
         <v>1.03</v>
@@ -610,7 +610,7 @@
         <v>2.24</v>
       </c>
       <c r="O2" t="n">
-        <v>6842847810</v>
+        <v>6918246210</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3895</v>
+        <v>3960</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+10.81%</t>
+          <t>'+12.66%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="H3" t="n">
         <v>3.11</v>
@@ -702,7 +702,7 @@
         <v>3.16</v>
       </c>
       <c r="O3" t="n">
-        <v>8370207734</v>
+        <v>8894089021</v>
       </c>
       <c r="P3" t="n">
         <v>16110</v>
@@ -711,23 +711,23 @@
         <v>2300</v>
       </c>
       <c r="R3" t="n">
-        <v>-371000</v>
+        <v>-383000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-140000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>25-26년 대규모 적자 예상 및 상폐 가능성 제기. 주가 하락 및 투자 경고 신호.</t>
+          <t>이뮨온시아는 25년 94억, 26년 95억 적자 예상으로 인한 상폐 우려 속에서 급등락을 반복. 일부 투자자는 공매도 세력의 움직임과 단기 급등을 경계하는 한편, 임상 성공에 대한 기대감도 일부 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['적자', '상폐', '하락']</t>
+          <t>['적자', '상폐', '임상']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4480</v>
+        <v>4460</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.74%</t>
+          <t>'+8.25%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="H4" t="n">
         <v>0.74</v>
@@ -794,7 +794,7 @@
         <v>0.77</v>
       </c>
       <c r="O4" t="n">
-        <v>153250673389</v>
+        <v>164776147085</v>
       </c>
       <c r="P4" t="n">
         <v>8100</v>
@@ -803,23 +803,23 @@
         <v>592</v>
       </c>
       <c r="R4" t="n">
-        <v>384000</v>
+        <v>188000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>광케이블 관련 미 증시 상승 수혜 및 4천원 지지선 언급. 7천원까지의 상승 가능성 및 외국인 매수세 기대.</t>
+          <t>AI 데이터센터 투자 수혜 기대감 속에서 주가 상승 시도. 외국인 동시호가 매수세 관찰.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['광케이블', '지지선', '외국인']</t>
+          <t>['AI', '데이터센터', '광통신']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한컴위드</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14820</v>
+        <v>5530</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.81%</t>
+          <t>'+5.74%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.15</v>
+        <v>-1.39</v>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="H5" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14140</v>
+        <v>5230</v>
       </c>
       <c r="K5" t="n">
-        <v>14420</v>
+        <v>5750</v>
       </c>
       <c r="L5" t="n">
-        <v>15250</v>
+        <v>5880</v>
       </c>
       <c r="M5" t="n">
-        <v>14300</v>
+        <v>5200</v>
       </c>
       <c r="N5" t="n">
-        <v>1.8</v>
+        <v>2.68</v>
       </c>
       <c r="O5" t="n">
-        <v>132543511315</v>
+        <v>40209818555</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>8980</v>
       </c>
       <c r="Q5" t="n">
-        <v>1272</v>
+        <v>2795</v>
       </c>
       <c r="R5" t="n">
-        <v>93000</v>
+        <v>259000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미 증시 통신장비주 강세에 따른 동반 상승 기대감. 14000원 지지선 확보 및 17000원 돌파 가능성 언급.</t>
+          <t>트럼프 양자암호 행정명령 및 미 보안주 상승에 따른 기대감. 스테이블 코인 법안 부결로 인한 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['통신장비', '지지선', '상승']</t>
+          <t>['양자암호', '보안', '스테이블코인']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,77 +924,77 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>054920</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1726000</v>
+        <v>14830</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.13%</t>
+          <t>'+4.88%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="E6" t="n">
-        <v>677</v>
+        <v>81</v>
       </c>
       <c r="F6" t="n">
-        <v>414</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>2010</v>
+        <v>349</v>
       </c>
       <c r="H6" t="n">
-        <v>50.2</v>
+        <v>1.95</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1690000</v>
+        <v>14140</v>
       </c>
       <c r="K6" t="n">
-        <v>1686000</v>
+        <v>14420</v>
       </c>
       <c r="L6" t="n">
-        <v>1729000</v>
+        <v>15250</v>
       </c>
       <c r="M6" t="n">
-        <v>1686000</v>
+        <v>14300</v>
       </c>
       <c r="N6" t="n">
-        <v>50.27</v>
+        <v>1.8</v>
       </c>
       <c r="O6" t="n">
-        <v>871408434500</v>
+        <v>143615972125</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>331500</v>
+        <v>1272</v>
       </c>
       <c r="R6" t="n">
-        <v>4000</v>
+        <v>324000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미 증시 반도체 선물 상승 및 인텔 CEO 발언에 대한 기대감 존재. 다만, 매크로 지표 및 반도체 주 하락 가능성에 대한 신중론도 제기됨.</t>
+          <t>광통신 및 통신 장비 섹터 강세에 따른 상승 기대감. 14000원 지지선 확보 후 반등 시도.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체', '선물', '전망']</t>
+          <t>['광통신', '통신 장비', '지지선']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>250500</v>
+        <v>3460</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.80%</t>
+          <t>'+2.98%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>-1.34</v>
       </c>
       <c r="E7" t="n">
-        <v>654</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>392</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>2252</v>
+        <v>112</v>
       </c>
       <c r="H7" t="n">
-        <v>46.56</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>248500</v>
+        <v>3360</v>
       </c>
       <c r="K7" t="n">
-        <v>248000</v>
+        <v>3570</v>
       </c>
       <c r="L7" t="n">
-        <v>251000</v>
+        <v>3910</v>
       </c>
       <c r="M7" t="n">
-        <v>247500</v>
+        <v>3345</v>
       </c>
       <c r="N7" t="n">
-        <v>46.57</v>
+        <v>1.34</v>
       </c>
       <c r="O7" t="n">
-        <v>469646632500</v>
+        <v>72390082232</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>5100</v>
       </c>
       <c r="Q7" t="n">
-        <v>76700</v>
+        <v>966</v>
       </c>
       <c r="R7" t="n">
-        <v>-375000</v>
+        <v>113000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈와 반도체 지수 상승 언급 외 구체적 근거 부족.</t>
+          <t>미국 양자내성암호 행정명령 관련 수혜 기대감. 매집 흔적 및 롤링 구간 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['양자암호', '보안', '매집']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3385</v>
+        <v>18040</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.74%</t>
+          <t>'+2.79%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.34</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3360</v>
+        <v>17550</v>
       </c>
       <c r="K8" t="n">
-        <v>3570</v>
+        <v>17150</v>
       </c>
       <c r="L8" t="n">
-        <v>3910</v>
+        <v>18160</v>
       </c>
       <c r="M8" t="n">
-        <v>3345</v>
+        <v>17020</v>
       </c>
       <c r="N8" t="n">
-        <v>1.34</v>
+        <v>0.35</v>
       </c>
       <c r="O8" t="n">
-        <v>69248669108</v>
+        <v>54200480110</v>
       </c>
       <c r="P8" t="n">
-        <v>5100</v>
+        <v>30550</v>
       </c>
       <c r="Q8" t="n">
-        <v>966</v>
+        <v>6100</v>
       </c>
       <c r="R8" t="n">
-        <v>592000</v>
+        <v>65000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>양자내성암호 관련 이슈 부각. 다만, 단기 급등 후 하락 가능성 및 분기 매출 부진에 대한 우려 제기.</t>
+          <t>미국 보안주 상승 마감에 따른 기대감. 상용화 및 매출 발생 기업 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['양자암호', '매출', '하락']</t>
+          <t>['보안', '상용화', '매출']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8500</v>
+        <v>1721000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.28%</t>
+          <t>'+1.83%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.5</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>52</v>
+        <v>712</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>431</v>
       </c>
       <c r="G9" t="n">
-        <v>128</v>
+        <v>2183</v>
       </c>
       <c r="H9" t="n">
-        <v>26.66</v>
+        <v>50.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8610</v>
+        <v>1690000</v>
       </c>
       <c r="K9" t="n">
-        <v>8600</v>
+        <v>1686000</v>
       </c>
       <c r="L9" t="n">
-        <v>8610</v>
+        <v>1731000</v>
       </c>
       <c r="M9" t="n">
-        <v>8460</v>
+        <v>1686000</v>
       </c>
       <c r="N9" t="n">
-        <v>27.16</v>
+        <v>50.27</v>
       </c>
       <c r="O9" t="n">
-        <v>4118565445</v>
+        <v>1036392852500</v>
       </c>
       <c r="P9" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>8120</v>
+        <v>331500</v>
       </c>
       <c r="R9" t="n">
-        <v>-150000</v>
+        <v>18000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>키움 리포트 기반 3분기 실적 하락 가능성 언급. 외인 매도세 및 높은 부채 비율 우려.</t>
+          <t>뉴욕증시 반도체 선물 급등 및 인텔 CEO 발언에 따른 상승 기대. 자사주 매입 및 소각 기대감 형성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['실적', '환율', '부채']</t>
+          <t>['반도체', '메모리', '자사주']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>84900</v>
+        <v>250750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.51%</t>
+          <t>'+0.91%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>93</v>
+        <v>704</v>
       </c>
       <c r="F10" t="n">
-        <v>64</v>
+        <v>410</v>
       </c>
       <c r="G10" t="n">
-        <v>418</v>
+        <v>2326</v>
       </c>
       <c r="H10" t="n">
-        <v>23.37</v>
+        <v>46.56</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>86200</v>
+        <v>248500</v>
       </c>
       <c r="K10" t="n">
-        <v>86200</v>
+        <v>248000</v>
       </c>
       <c r="L10" t="n">
-        <v>86300</v>
+        <v>251500</v>
       </c>
       <c r="M10" t="n">
-        <v>84400</v>
+        <v>247500</v>
       </c>
       <c r="N10" t="n">
-        <v>23.45</v>
+        <v>46.57</v>
       </c>
       <c r="O10" t="n">
-        <v>39105566550</v>
+        <v>562206728250</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>76700</v>
       </c>
       <c r="R10" t="n">
-        <v>-82000</v>
+        <v>-496000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>웨스팅하우스 지분 인수 가능성에 대한 기대감과 공매도 관련 우려가 혼재. 대규모 상승 가능성 언급.</t>
+          <t>정치적 이슈와 반도체 지수 상승 언급 외 구체적 근거 부족.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['지분 인수', '공매도', '전망']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>107</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14700</v>
+        <v>8530</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.87%</t>
+          <t>'-0.93%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E11" t="n">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>363</v>
+        <v>152</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>26.66</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14980</v>
+        <v>8610</v>
       </c>
       <c r="K11" t="n">
-        <v>15300</v>
+        <v>8600</v>
       </c>
       <c r="L11" t="n">
-        <v>15580</v>
+        <v>8610</v>
       </c>
       <c r="M11" t="n">
-        <v>14610</v>
+        <v>8460</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>27.16</v>
       </c>
       <c r="O11" t="n">
-        <v>16218854420</v>
+        <v>4478214505</v>
       </c>
       <c r="P11" t="n">
-        <v>36200</v>
+        <v>17950</v>
       </c>
       <c r="Q11" t="n">
-        <v>8920</v>
+        <v>8120</v>
       </c>
       <c r="R11" t="n">
-        <v>-49000</v>
+        <v>-292000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국제유가 상승 및 이란 관련 지정학적 리스크 부각. 1만 5천원대 이상 상승 여력 기대.</t>
+          <t>환율 및 단가 인하 요인으로 인한 3분기 실적 일시적 하락 전망. 외인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적 리스크', '상승']</t>
+          <t>['실적', '환율', '외인']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31650</v>
+        <v>14770</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.47%</t>
+          <t>'-1.40%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="F12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G12" t="n">
-        <v>599</v>
+        <v>363</v>
       </c>
       <c r="H12" t="n">
-        <v>17.16</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,28 +1515,28 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>32450</v>
+        <v>14980</v>
       </c>
       <c r="K12" t="n">
-        <v>32850</v>
+        <v>15300</v>
       </c>
       <c r="L12" t="n">
-        <v>32850</v>
+        <v>15580</v>
       </c>
       <c r="M12" t="n">
-        <v>31550</v>
+        <v>14600</v>
       </c>
       <c r="N12" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3010157300</v>
+        <v>17180895770</v>
       </c>
       <c r="P12" t="n">
-        <v>69200</v>
+        <v>36200</v>
       </c>
       <c r="Q12" t="n">
-        <v>24150</v>
+        <v>8920</v>
       </c>
       <c r="R12" t="n">
         <v>-19000</v>
@@ -1546,20 +1546,20 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>간암 신약 관련 유럽 신청 결과 및 FDA 승인 실패 가능성에 대한 우려. 과거 실패 사례 및 주가 하락 가능성 언급.</t>
+          <t>국제 유가 상승 및 중동 지역 지정학적 리스크 부각에 따른 유가 관련주 강세 기대. 비축유 이슈 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['신약', 'FDA', '실패']</t>
+          <t>['국제유가', '지정학적 리스크', '에너지']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5740</v>
+        <v>84900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-9.03%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-2.04</v>
+        <v>-0.08</v>
       </c>
       <c r="E13" t="n">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="F13" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="G13" t="n">
-        <v>112</v>
+        <v>428</v>
       </c>
       <c r="H13" t="n">
-        <v>0.98</v>
+        <v>23.37</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6310</v>
+        <v>86200</v>
       </c>
       <c r="K13" t="n">
-        <v>6390</v>
+        <v>86200</v>
       </c>
       <c r="L13" t="n">
-        <v>6450</v>
+        <v>86300</v>
       </c>
       <c r="M13" t="n">
-        <v>5630</v>
+        <v>84400</v>
       </c>
       <c r="N13" t="n">
-        <v>3.02</v>
+        <v>23.45</v>
       </c>
       <c r="O13" t="n">
-        <v>25798576330</v>
+        <v>42509871000</v>
       </c>
       <c r="P13" t="n">
-        <v>11370</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>3300</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>213000</v>
+        <v>-105000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-21000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미 클래리티법 부결 및 이스타항공 공급 계약 소식에도 불구하고, 삼성과의 공급 계약 규모 및 가상자산 시장 약세 영향.</t>
+          <t>웨스팅하우스 지분 인수 가능성에 대한 기대감과 공매도 관련 우려가 혼재. 대규모 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,18 +1647,386 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>['지분 인수', '공매도', '전망']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>광전자</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>10430</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-2.16%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E14" t="n">
+        <v>42</v>
+      </c>
+      <c r="F14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G14" t="n">
+        <v>86</v>
+      </c>
+      <c r="H14" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>10660</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10500</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10900</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10060</v>
+      </c>
+      <c r="N14" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="O14" t="n">
+        <v>62524612165</v>
+      </c>
+      <c r="P14" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1760</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-437000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>AI 데이터센터 투자 수혜 언급에도 불구하고 하락세. 외국인 매수세 관찰.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['AI', '데이터센터', '투자']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>017900</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>18645</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-2.54%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E15" t="n">
+        <v>46</v>
+      </c>
+      <c r="F15" t="n">
+        <v>37</v>
+      </c>
+      <c r="G15" t="n">
+        <v>198</v>
+      </c>
+      <c r="H15" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>19130</v>
+      </c>
+      <c r="K15" t="n">
+        <v>19160</v>
+      </c>
+      <c r="L15" t="n">
+        <v>19340</v>
+      </c>
+      <c r="M15" t="n">
+        <v>18640</v>
+      </c>
+      <c r="N15" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="O15" t="n">
+        <v>20473589715</v>
+      </c>
+      <c r="P15" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-112000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>대차 해지 운동 독려하며 주가 상승 기대감 표출. 명분 없는 파병 이슈 언급.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['대차 해지', '주주 운동', '상승 기대']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>31250</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>'-3.70%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="E16" t="n">
+        <v>113</v>
+      </c>
+      <c r="F16" t="n">
+        <v>75</v>
+      </c>
+      <c r="G16" t="n">
+        <v>630</v>
+      </c>
+      <c r="H16" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>32450</v>
+      </c>
+      <c r="K16" t="n">
+        <v>32850</v>
+      </c>
+      <c r="L16" t="n">
+        <v>32850</v>
+      </c>
+      <c r="M16" t="n">
+        <v>31250</v>
+      </c>
+      <c r="N16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3710923900</v>
+      </c>
+      <c r="P16" t="n">
+        <v>69200</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>24150</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-26000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>HLB의 유럽 담관암 신약 신청 시점과 관련하여 FDA 승인 실패 가능성 및 제약 실권주 공모와의 연관성에 대한 의문 제기. 과거 신약 실패 경험을 근거로 하방 베팅 의견과 함께, 유럽 신청이 FDA 승인에 대한 자신감 표현이라는 반대 의견 혼재.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['담관암', '유럽 신청', 'FDA 승인']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>아톤</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5910</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>'-6.34%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="E17" t="n">
+        <v>71</v>
+      </c>
+      <c r="F17" t="n">
+        <v>43</v>
+      </c>
+      <c r="G17" t="n">
+        <v>120</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>6310</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6390</v>
+      </c>
+      <c r="L17" t="n">
+        <v>6450</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5630</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O17" t="n">
+        <v>31188626985</v>
+      </c>
+      <c r="P17" t="n">
+        <v>11370</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3300</v>
+      </c>
+      <c r="R17" t="n">
+        <v>247000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>미 클래리티법 부결 및 이스타항공 공급 계약 소식에도 불구하고, 삼성과의 공급 계약 규모 및 가상자산 시장 약세 영향.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>['양자내성암호', '공급계약', '가상자산']</t>
         </is>
       </c>
-      <c r="X13" t="n">
+      <c r="X17" t="n">
         <v>2</v>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>158430</t>
         </is>
